--- a/data/regional_comprehensive_support_center/data.xlsx
+++ b/data/regional_comprehensive_support_center/data.xlsx
@@ -486,7 +486,7 @@
         <v>134.04093382459948</v>
       </c>
       <c r="D3" t="str">
-        <v>地域包括支援センターサブセンター仏生山（仏生山交流センター1階）</v>
+        <v>地域包括支援センターサブセンター仏生山（仏生山交流センター内）</v>
       </c>
       <c r="E3" t="str">
         <v>高松市仏生山町甲218-1</v>
